--- a/results/naturverbundenheit/explaining_features/nature-dataset-optimal_explainable_feature_importances-jensenshannon-auto.xlsx
+++ b/results/naturverbundenheit/explaining_features/nature-dataset-optimal_explainable_feature_importances-jensenshannon-auto.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2587302436106365</v>
+        <v>0.0482473443929697</v>
       </c>
     </row>
     <row r="3">
@@ -452,17 +452,57 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3616734702405453</v>
+        <v>0.1919720445358652</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>['GI']</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.07308696018600963</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>['HDI', 'LPI']</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.3795962861488182</v>
+      <c r="B5" t="n">
+        <v>0.1752225319440224</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>['HDI', 'GI']</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1449646022689428</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>['LPI', 'GI']</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.1815309357558823</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>['HDI', 'LPI', 'GI']</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.184975580916308</v>
       </c>
     </row>
   </sheetData>
